--- a/docs/estructuras/tema2/estructuras_qfdos.xlsx
+++ b/docs/estructuras/tema2/estructuras_qfdos.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Estructuras" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Propiedades'!$A$1:$AF$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Propiedades'!$A$1:$AF$82</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1367,6 +1367,806 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>53</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>55</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>56</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>58</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>63</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>64</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>68</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>70</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>71</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>73</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>74</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>75</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>77</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>78</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>79</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>80</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>81</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="1905000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1659,7 +2459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF50"/>
+  <dimension ref="A1:AF82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4106,12 +4906,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CN[C@@H](C)[C@@H](O)c1ccccc1</t>
+          <t>CN[C@@H](C)[C@H](O)c1ccccc1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>C[NH2+][C@@H](C)[C@@H](O)c1ccccc1</t>
+          <t>C[NH2+][C@@H](C)[C@H](O)c1ccccc1</t>
         </is>
       </c>
       <c r="J19" t="n">
@@ -4119,7 +4919,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>CN[C@@H](C)[C@@H](O)c1ccccc1</t>
+          <t>CN[C@@H](C)[C@H](O)c1ccccc1</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -4171,12 +4971,12 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>C3:S; C5:S</t>
+          <t>C3:S; C5:R</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>KWGRBVOPPLSCSI-WCBMZHEXSA-N</t>
+          <t>KWGRBVOPPLSCSI-WPRPVWTQSA-N</t>
         </is>
       </c>
       <c r="AC19" t="n">
@@ -4236,12 +5036,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CN[C@@H](C)[C@H](O)c1ccccc1</t>
+          <t>CN[C@@H](C)[C@@H](O)c1ccccc1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>C[NH2+][C@@H](C)[C@H](O)c1ccccc1</t>
+          <t>C[NH2+][C@@H](C)[C@@H](O)c1ccccc1</t>
         </is>
       </c>
       <c r="J20" t="n">
@@ -4249,7 +5049,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>CN[C@@H](C)[C@H](O)c1ccccc1</t>
+          <t>CN[C@@H](C)[C@@H](O)c1ccccc1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -4301,12 +5101,12 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>C3:S; C5:R</t>
+          <t>C3:S; C5:S</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>KWGRBVOPPLSCSI-WPRPVWTQSA-N</t>
+          <t>KWGRBVOPPLSCSI-WCBMZHEXSA-N</t>
         </is>
       </c>
       <c r="AC20" t="n">
@@ -4626,12 +5426,12 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>C[C@@H](N)Cc1ccccc1</t>
+          <t>C[C@H](N)Cc1ccccc1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>C[C@@H]([NH3+])Cc1ccccc1</t>
+          <t>C[C@H]([NH3+])Cc1ccccc1</t>
         </is>
       </c>
       <c r="J23" t="n">
@@ -4639,7 +5439,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>C[C@@H](N)Cc1ccccc1</t>
+          <t>C[C@H](N)Cc1ccccc1</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -4691,12 +5491,12 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>C2:R</t>
+          <t>C2:S</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>KWTSXDURSIMDCE-MRVPVSSYSA-N</t>
+          <t>KWTSXDURSIMDCE-QMMMGPOBSA-N</t>
         </is>
       </c>
       <c r="AC23" t="n">
@@ -6958,12 +7758,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>C1CCN(CC2Oc3ccccc3O2)CC1</t>
+          <t>C1CCN(CC2COc3ccccc3O2)CC1</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>C1CC[NH+](CC2Oc3ccccc3O2)CC1</t>
+          <t>C1CC[NH+](CC2COc3ccccc3O2)CC1</t>
         </is>
       </c>
       <c r="J41" t="n">
@@ -6971,28 +7771,28 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>c1ccc2c(c1)OC(CN1CCCCC1)O2</t>
+          <t>c1ccc2c(c1)OCC(CN1CCCCC1)O2</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>C13H17NO2</t>
+          <t>C14H19NO2</t>
         </is>
       </c>
       <c r="M41" t="n">
-        <v>219.28</v>
+        <v>233.31</v>
       </c>
       <c r="N41" t="n">
-        <v>219.1259</v>
+        <v>233.1416</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="Q41" t="n">
-        <v>61.78</v>
+        <v>66.64</v>
       </c>
       <c r="R41" t="n">
         <v>21.7</v>
@@ -7007,7 +7807,7 @@
         <v>2</v>
       </c>
       <c r="V41" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="W41" t="n">
         <v>3</v>
@@ -7016,19 +7816,19 @@
         <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>0.538</v>
+        <v>0.571</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.761</v>
+        <v>0.782</v>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>aquiral</t>
+          <t>1 centro(s) sin definir</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>IYNDAZPVMKHILR-UHFFFAOYSA-N</t>
+          <t>LYKMMUBOEFYJQG-UHFFFAOYSA-N</t>
         </is>
       </c>
       <c r="AC41" t="n">
@@ -7081,15 +7881,19 @@
           <t>63-01-4</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>CHEMBL3248383</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CCN(CC)C[C@@H]1Oc2ccccc2O1</t>
+          <t>CCN(CC)C[C@H]1COc2ccccc2O1</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CC[NH+](CC)C[C@@H]1Oc2ccccc2O1</t>
+          <t>CC[NH+](CC)C[C@H]1COc2ccccc2O1</t>
         </is>
       </c>
       <c r="J42" t="n">
@@ -7097,28 +7901,28 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>CCN(CC)CC1Oc2ccccc2O1</t>
+          <t>CCN(CC)C[C@H]1COc2ccccc2O1</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>C12H17NO2</t>
+          <t>C13H19NO2</t>
         </is>
       </c>
       <c r="M42" t="n">
-        <v>207.27</v>
+        <v>221.3</v>
       </c>
       <c r="N42" t="n">
-        <v>207.1259</v>
+        <v>221.1416</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="Q42" t="n">
-        <v>59.27</v>
+        <v>64.14</v>
       </c>
       <c r="R42" t="n">
         <v>21.7</v>
@@ -7133,7 +7937,7 @@
         <v>4</v>
       </c>
       <c r="V42" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W42" t="n">
         <v>2</v>
@@ -7142,19 +7946,19 @@
         <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>0.5</v>
+        <v>0.538</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.755</v>
+        <v>0.777</v>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>aquiral</t>
+          <t>C7:S</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>MZQSVWMQXWKBQC-UHFFFAOYSA-N</t>
+          <t>BGWGNDUTMDMIKZ-NSHDSACASA-N</t>
         </is>
       </c>
       <c r="AC42" t="n">
@@ -7207,15 +8011,19 @@
           <t>63-01-4</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>CHEMBL3248384</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CCN(CC)C[C@H]1Oc2ccccc2O1</t>
+          <t>CCN(CC)C[C@@H]1COc2ccccc2O1</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CC[NH+](CC)C[C@H]1Oc2ccccc2O1</t>
+          <t>CC[NH+](CC)C[C@@H]1COc2ccccc2O1</t>
         </is>
       </c>
       <c r="J43" t="n">
@@ -7223,28 +8031,28 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>CCN(CC)CC1Oc2ccccc2O1</t>
+          <t>CCN(CC)C[C@@H]1COc2ccccc2O1</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>C12H17NO2</t>
+          <t>C13H19NO2</t>
         </is>
       </c>
       <c r="M43" t="n">
-        <v>207.27</v>
+        <v>221.3</v>
       </c>
       <c r="N43" t="n">
-        <v>207.1259</v>
+        <v>221.1416</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="Q43" t="n">
-        <v>59.27</v>
+        <v>64.14</v>
       </c>
       <c r="R43" t="n">
         <v>21.7</v>
@@ -7259,7 +8067,7 @@
         <v>4</v>
       </c>
       <c r="V43" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="W43" t="n">
         <v>2</v>
@@ -7268,19 +8076,19 @@
         <v>1</v>
       </c>
       <c r="Y43" t="n">
-        <v>0.5</v>
+        <v>0.538</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.755</v>
+        <v>0.777</v>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>aquiral</t>
+          <t>C7:R</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>MZQSVWMQXWKBQC-UHFFFAOYSA-N</t>
+          <t>BGWGNDUTMDMIKZ-LLVKDONJSA-N</t>
         </is>
       </c>
       <c r="AC43" t="n">
@@ -8204,8 +9012,4008 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>QFDOS-095</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1,2-Diclorobenceno</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1,2-Dichlorobenzene</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores beta</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Reactivo: areno</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>95-50-1</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ClC1=C(C=CC=C1)Cl</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>ClC1=C(C=CC=C1)Cl</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Clc1ccccc1Cl</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>C6H4Cl2</t>
+        </is>
+      </c>
+      <c r="M51" t="n">
+        <v>147</v>
+      </c>
+      <c r="N51" t="n">
+        <v>145.969</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>36.46</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>8</v>
+      </c>
+      <c r="W51" t="n">
+        <v>1</v>
+      </c>
+      <c r="X51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>RFFLAFLAYFXFSW-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>img/QFDOS-095_1_2_diclorobenceno.png</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>Paso 1 de la síntesis del DCI (QFDOS-080). Sustrato de la acilación de Friedel-Crafts. Los dos Cl desactivan el anillo pero orientan orto/para; la acilación entra en para respecto a un Cl (posición 4) por impedimento estérico, fijando el patrón 3,4-dicloro del producto final.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>QFDOS-096</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cloruro de acetilo</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Acetyl chloride</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores beta</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Reactivo: agente acilante</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>75-36-5</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>CC(Cl)=O</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>CC(Cl)=O</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>CC(=O)Cl</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>C2H3ClO</t>
+        </is>
+      </c>
+      <c r="M52" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="N52" t="n">
+        <v>77.9872</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="R52" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>4</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>WETWJCDKMRHUPV-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>img/QFDOS-096_cloruro_de_acetilo.png</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>Paso 1. Agente acilante de Friedel-Crafts con AlCl3: genera el ion acilio CH3CO+ que ataca al 1,2-diclorobenceno. Aporta los dos carbonos de la cadena etanolamínica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>QFDOS-097</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>3,4-Dicloroacetofenona</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3,4-Dichloroacetophenone</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores beta</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Intermedio de sintesis</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2642-63-9</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ClC2=C(C=CC(C(C)=O)=C2)Cl</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>ClC2=C(C=CC(C(C)=O)=C2)Cl</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>CC(=O)c1ccc(Cl)c(Cl)c1</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>C8H6Cl2O</t>
+        </is>
+      </c>
+      <c r="M53" t="n">
+        <v>189.04</v>
+      </c>
+      <c r="N53" t="n">
+        <v>187.9796</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>46.47</v>
+      </c>
+      <c r="R53" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
+      </c>
+      <c r="V53" t="n">
+        <v>11</v>
+      </c>
+      <c r="W53" t="n">
+        <v>1</v>
+      </c>
+      <c r="X53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>WBPAOUHWPONFEQ-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>img/QFDOS-097_3_4_dicloroacetofenona.png</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>Producto del paso 1 (Friedel-Crafts). Aril metil cetona; el metilo alfa al carbonilo es enolizable y es el punto de entrada del bromo en el paso 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>QFDOS-098</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Bromo</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Bromine</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores beta</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Reactivo: halogenante</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>7726-95-6</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>BrBr</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>BrBr</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>BrBr</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Br2</t>
+        </is>
+      </c>
+      <c r="M54" t="n">
+        <v>159.81</v>
+      </c>
+      <c r="N54" t="n">
+        <v>157.8367</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>2</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>GDTBXPJZTBHREO-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>img/QFDOS-098_bromo.png</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>Paso 2. Alfa-bromación de la cetona vía enol (medio ácido, AcOH o Et2O). Introduce el grupo saliente sobre el carbono que llevará después el nitrógeno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>QFDOS-099</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2-Bromo-3,4-dicloroacetofenona</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2-Bromo-1-(3,4-dichlorophenyl)ethanone</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores beta</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Intermedio de sintesis</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2632-10-2</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ClC3=C(C=CC(C(CBr)=O)=C3)Cl</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>ClC3=C(C=CC(C(CBr)=O)=C3)Cl</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>O=C(CBr)c1ccc(Cl)c(Cl)c1</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>C8H5BrCl2O</t>
+        </is>
+      </c>
+      <c r="M55" t="n">
+        <v>267.94</v>
+      </c>
+      <c r="N55" t="n">
+        <v>265.8901</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>54.59</v>
+      </c>
+      <c r="R55" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
+      </c>
+      <c r="V55" t="n">
+        <v>12</v>
+      </c>
+      <c r="W55" t="n">
+        <v>1</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>0.591</v>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>PAKFHEFMTRCFAU-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>img/QFDOS-099_2_bromo_3_4_dicloroacetofenona.png</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>Producto del paso 2. alfa-Bromocetona (fenacilo), electrófilo muy reactivo y lacrimógeno. Se reduce el carbonilo antes de introducir la amina para evitar la autocondensación de la aminocetona.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>QFDOS-100</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2-Bromo-1-(3,4-diclorofenil)etanol</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2-Bromo-1-(3,4-dichlorophenyl)ethanol</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores beta</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Intermedio de sintesis</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ClC4=C(C=CC(C(CBr)O)=C4)Cl</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>ClC4=C(C=CC(C(CBr)O)=C4)Cl</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>OC(CBr)c1ccc(Cl)c(Cl)c1</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>C8H7BrCl2O</t>
+        </is>
+      </c>
+      <c r="M56" t="n">
+        <v>269.95</v>
+      </c>
+      <c r="N56" t="n">
+        <v>267.9057</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="R56" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="S56" t="n">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
+      </c>
+      <c r="V56" t="n">
+        <v>12</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1</v>
+      </c>
+      <c r="X56" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>1 centro(s) sin definir</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>ZFMARCNWWLHGAZ-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>img/QFDOS-100_2_bromo_1_3_4_diclorofenil_etanol.png</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>Producto del paso 3 (reducción del carbonilo, p. ej. NaBH4). Bromhidrina racémica: crea el estereocentro bencílico del DCI sin control estereoquímico, de ahí que el producto se obtenga racémico. En medio básico cicla al epóxido (óxido de estireno), que es el electrófilo real en el paso 4. CAS no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>QFDOS-101</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Isopropilamina</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Isopropylamine</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores beta</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Reactivo: amina nucleófila</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>75-31-0</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>CC(C)N</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>CC(C)[NH3+]</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>CC(C)N</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>C3H9N</t>
+        </is>
+      </c>
+      <c r="M57" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="N57" t="n">
+        <v>59.0735</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="R57" t="n">
+        <v>26.02</v>
+      </c>
+      <c r="S57" t="n">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" t="n">
+        <v>4</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z57" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>JJWLVOIRVHMVIS-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>img/QFDOS-101_isopropilamina.png</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>Paso 4. Nucleófilo que desplaza el bromuro (o abre el epóxido por el carbono menos sustituido) y aporta el N-isopropilo, el sustituyente que confiere selectividad beta, heredado de la isoprenalina. Producto: DCI (QFDOS-080). pKa ≈ 10.6, protonada a pH 7.4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>QFDOS-102</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2-Acetilnaftaleno</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2-Acetonaphthone</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores beta</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Reactivo: aril metil cetona</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>93-08-3</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>CHEMBL3183700</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>CC(C1=CC2=CC=CC=C2C=C1)=O</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>CC(C1=CC2=CC=CC=C2C=C1)=O</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>CC(=O)c1ccc2ccccc2c1</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>C12H10O</t>
+        </is>
+      </c>
+      <c r="M58" t="n">
+        <v>170.21</v>
+      </c>
+      <c r="N58" t="n">
+        <v>170.0732</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="R58" t="n">
+        <v>17.07</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" t="n">
+        <v>13</v>
+      </c>
+      <c r="W58" t="n">
+        <v>2</v>
+      </c>
+      <c r="X58" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y58" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="Z58" t="n">
+        <v>0.601</v>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>XSAYZAUNJMRRIR-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>img/QFDOS-102_2_acetilnaftaleno.png</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>Metil 2-naftil cetona. Material de partida del pronetalol (QFDOS-081) por la misma secuencia que el DCI: alfa-bromación (QFDOS-098) a 2-bromoacetonaftona, aminación con isopropilamina (QFDOS-101) y reducción del carbonilo. Equivale a la 3,4-dicloroacetofenona (QFDOS-097) con el naftaleno como bioisóstero lipófilo del anillo 3,4-diclorofenilo: el naftilo elimina la actividad agonista parcial del DCI. Sin ionización a pH 7.4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>QFDOS-103</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1-Naftol</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1-Naphthol</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores beta</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Reactivo: fenol</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>CHEMBL122617</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>OC1=CC=CC2=C1C=CC=C2</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>OC1=CC=CC2=C1C=CC=C2</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Oc1cccc2ccccc12</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>C10H8O</t>
+        </is>
+      </c>
+      <c r="M59" t="n">
+        <v>144.17</v>
+      </c>
+      <c r="N59" t="n">
+        <v>144.0575</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>45.61</v>
+      </c>
+      <c r="R59" t="n">
+        <v>20.23</v>
+      </c>
+      <c r="S59" t="n">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" t="n">
+        <v>11</v>
+      </c>
+      <c r="W59" t="n">
+        <v>2</v>
+      </c>
+      <c r="X59" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>KJCVRFUGPWSIIH-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>img/QFDOS-103_1_naftol.png</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>Paso 1 de la síntesis del propranolol (QFDOS-082/083). Fenol nucleófilo: en medio básico (NaOH o K2CO3) el naftóxido ataca a la epiclorhidrina. El naftilo se une por oxígeno, no por carbono como en el pronetalol (QFDOS-081): ese OCH2 extra es el salto de ariletanolamina a ariloxipropanolamina. pKa ≈ 9.3, neutro a pH 7.4. CAS no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>QFDOS-104</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Epiclorhidrina</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Epichlorohydrin</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores beta</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Reactivo: electrófilo bifuncional</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>CHEMBL1421613</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>ClCC1CO1</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>ClCC1CO1</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ClCC1CO1</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>C3H5ClO</t>
+        </is>
+      </c>
+      <c r="M60" t="n">
+        <v>92.53</v>
+      </c>
+      <c r="N60" t="n">
+        <v>92.0029</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>20.46</v>
+      </c>
+      <c r="R60" t="n">
+        <v>12.53</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
+      </c>
+      <c r="V60" t="n">
+        <v>5</v>
+      </c>
+      <c r="W60" t="n">
+        <v>1</v>
+      </c>
+      <c r="X60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>1 centro(s) sin definir</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>BRLQWZUYTZBJKN-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>img/QFDOS-104_epiclorhidrina.png</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>Paso 1. 2-(Clorometil)oxirano, electrófilo con dos puntos de ataque (C-Cl y epóxido). Aporta los tres carbonos de la cadena oxipropanolamina. Se usa racémica, de modo que el propranolol sale racémico; la (S)- o (R)-epiclorhidrina o el glicidol quiral dan acceso directo al eutómero (S). Alquilante y carcinógeno. CAS no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>QFDOS-105</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1-Naftil glicidil éter</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Glycidyl 1-naphthyl ether</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores beta</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Intermedio de sintesis</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>CHEMBL1929345</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>C4(C=CC=C5OCC6CO6)=C5C=CC=C4</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>C4(C=CC=C5OCC6CO6)=C5C=CC=C4</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>c1ccc2c(OCC3CO3)cccc2c1</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>C13H12O2</t>
+        </is>
+      </c>
+      <c r="M61" t="n">
+        <v>200.24</v>
+      </c>
+      <c r="N61" t="n">
+        <v>200.0837</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>59.18</v>
+      </c>
+      <c r="R61" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>3</v>
+      </c>
+      <c r="V61" t="n">
+        <v>15</v>
+      </c>
+      <c r="W61" t="n">
+        <v>3</v>
+      </c>
+      <c r="X61" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>1 centro(s) sin definir</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>QYYCPWLLBSSFBW-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>img/QFDOS-105_1_naftil_glicidil_eter.png</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>2-[(Naftalen-1-iloxi)metil]oxirano. Producto del paso 1, por sustitución del cloruro o por apertura del epóxido seguida de recierre: el resultado es el mismo glicidil éter. Paso 2: la isopropilamina (QFDOS-101) abre el epóxido por el carbono terminal, menos impedido (SN2), y da el propranolol racémico. El estereocentro del epóxido pasa al carbinol del fármaco. CAS no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>QFDOS-106</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Catecol</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Catechol</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores alfa</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Reactivo: difenol</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>CHEMBL280998</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>OC1=CC=CC=C1O</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>OC1=CC=CC=C1O</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Oc1ccccc1O</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>C6H6O2</t>
+        </is>
+      </c>
+      <c r="M62" t="n">
+        <v>110.11</v>
+      </c>
+      <c r="N62" t="n">
+        <v>110.0368</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="R62" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="S62" t="n">
+        <v>2</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" t="n">
+        <v>8</v>
+      </c>
+      <c r="W62" t="n">
+        <v>1</v>
+      </c>
+      <c r="X62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>YCIMNLLNPGFGHC-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>img/QFDOS-106_catecol.png</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>Paso 1 de la síntesis del piperoxano (QFDOS-085) y del prosimpal (QFDOS-086/087). 1,2-Dihidroxibenceno: en medio básico, los dos fenóxidos atacan a la epiclorhidrina (QFDOS-104), primero por SN2 o apertura del epóxido y después por cierre intramolecular, y forman el anillo de 1,4-benzodioxano. pKa1 ≈ 9.4, neutro a pH 7.4. CAS no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>QFDOS-107</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2-Hidroximetil-1,4-benzodioxano</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>(2,3-Dihydro-1,4-benzodioxin-2-yl)methanol</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores alfa</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Intermedio de sintesis</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>OCC1COC2=CC=CC=C2O1</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>OCC1COC2=CC=CC=C2O1</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>OCC1COc2ccccc2O1</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>C9H10O3</t>
+        </is>
+      </c>
+      <c r="M63" t="n">
+        <v>166.18</v>
+      </c>
+      <c r="N63" t="n">
+        <v>166.063</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="R63" t="n">
+        <v>38.69</v>
+      </c>
+      <c r="S63" t="n">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
+      </c>
+      <c r="V63" t="n">
+        <v>12</v>
+      </c>
+      <c r="W63" t="n">
+        <v>2</v>
+      </c>
+      <c r="X63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>0.671</v>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>1 centro(s) sin definir</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>GWQOQQVKVOOHTI-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>img/QFDOS-107_2_hidroximetil_1_4_benzodioxano.png</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>Producto del paso 1 (catecol + epiclorhidrina). Alcohol primario sobre el C2 del benzodioxano; el estereocentro C2 se forma sin control y el producto es racémico. Paso 2: se activa como cloruro (SOCl2) o tosilato. Sin entrada en ChEMBL: estructura validada con RDKit por coherencia con el piperoxano de ChEMBL (CHEMBL31836). CAS no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>QFDOS-108</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2-Clorometil-1,4-benzodioxano</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2-(Chloromethyl)-2,3-dihydro-1,4-benzodioxine</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores alfa</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Intermedio de sintesis</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ClCC1COC2=CC=CC=C2O1</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>ClCC1COC2=CC=CC=C2O1</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>ClCC1COc2ccccc2O1</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>C9H9ClO2</t>
+        </is>
+      </c>
+      <c r="M64" t="n">
+        <v>184.62</v>
+      </c>
+      <c r="N64" t="n">
+        <v>184.0291</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="P64" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>47.07</v>
+      </c>
+      <c r="R64" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
+      </c>
+      <c r="V64" t="n">
+        <v>12</v>
+      </c>
+      <c r="W64" t="n">
+        <v>2</v>
+      </c>
+      <c r="X64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y64" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Z64" t="n">
+        <v>0.622</v>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>1 centro(s) sin definir</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>AYPKYQSHFKQVDL-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>img/QFDOS-108_2_clorometil_1_4_benzodioxano.png</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>Producto del paso 2. Electrófilo de la aminación final (SN2 sobre CH2Cl primario). Con piperidina (QFDOS-109) da el piperoxano; con dietilamina da el prosimpal. Mismo esqueleto, solo cambia la amina: es el par SAR del bloque. Sin entrada en ChEMBL; validado con RDKit. CAS no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>QFDOS-109</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Piperidina</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Piperidine</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Sintesis de bloqueadores alfa</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Reactivo: amina nucleófila</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>CHEMBL15487</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>C1CNCCC1</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>C1C[NH2+]CCC1</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>C1CCNCC1</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>C5H11N</t>
+        </is>
+      </c>
+      <c r="M65" t="n">
+        <v>85.15000000000001</v>
+      </c>
+      <c r="N65" t="n">
+        <v>85.0891</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>26.72</v>
+      </c>
+      <c r="R65" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" t="n">
+        <v>6</v>
+      </c>
+      <c r="W65" t="n">
+        <v>1</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>NQRYJNQNLNOLGT-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>img/QFDOS-109_piperidina.png</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>Paso 3. Amina secundaria cíclica que desplaza el cloruro de QFDOS-108 y da el piperoxano (QFDOS-085). pKa ≈ 11.1, protonada a pH 7.4: el amonio resultante es el catión que interacciona con el Asp del receptor alfa. CAS no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>QFDOS-110</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ácido acetilsalicílico (Aspirina)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Aspirin</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Sintesis del salbutamol</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Material de partida</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>50-78-2</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>CHEMBL25</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>CC(=O)Oc1ccccc1C(=O)O</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>CC(=O)Oc1ccccc1C(=O)[O-]</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>CC(=O)Oc1ccccc1C(=O)O</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>C9H8O4</t>
+        </is>
+      </c>
+      <c r="M66" t="n">
+        <v>180.16</v>
+      </c>
+      <c r="N66" t="n">
+        <v>180.0423</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="R66" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="S66" t="n">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>3</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
+      </c>
+      <c r="V66" t="n">
+        <v>13</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1</v>
+      </c>
+      <c r="X66" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>BSYNRYMUTXBXSQ-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC66" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>img/QFDOS-110_acido_acetilsalicilico_aspirina.png</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>Material de partida de la síntesis industrial del salbutamol (QFDOS-074). Éster fenólico con un carboxilo en orto: los dos grupos que la ruta va a transformar ya están presentes. El acetilo del éster migrará al anillo en la transposición de Fries y el carboxilo acabará reducido al hidroximetilo característico del fármaco. pKa ≈ 3.5, carboxilato a pH 7.4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>QFDOS-111</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Ácido 5-acetil-2-hidroxibenzoico</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>5-Acetylsalicylic acid</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Sintesis del salbutamol</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Intermedio de sintesis</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>CC(=O)c1ccc(O)c(C(=O)O)c1</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>CC(=O)c1ccc(O)c(C(=O)[O-])c1</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>CC(=O)c1ccc(O)c(C(=O)O)c1</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>C9H8O4</t>
+        </is>
+      </c>
+      <c r="M67" t="n">
+        <v>180.16</v>
+      </c>
+      <c r="N67" t="n">
+        <v>180.0423</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="R67" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="S67" t="n">
+        <v>2</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
+      </c>
+      <c r="V67" t="n">
+        <v>13</v>
+      </c>
+      <c r="W67" t="n">
+        <v>1</v>
+      </c>
+      <c r="X67" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>NZRDKNBIPVLNHA-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC67" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>img/QFDOS-111_acido_5_acetil_2_hidroxibenzoico.png</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>Producto del paso 1: transposición de Fries sobre el ácido acetilsalicílico (QFDOS-110) con AlCl3 en nitrobenceno. El acilo pasa del oxígeno fenólico al carbono aromático, en posición para respecto a ese oxígeno, y se regenera el fenol libre. La metilcetona aromática recién instalada es el punto de anclaje de toda la cadena etanolamínica posterior. Sin entrada en ChEMBL; validado con RDKit. CAS no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>QFDOS-112</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5-Acetilsalicilato de metilo</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Methyl 5-acetylsalicylate</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Sintesis del salbutamol</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Intermedio de sintesis</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>CC(=O)c1ccc(O)c(C(=O)OC)c1</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>CC(=O)c1ccc(O)c(C(=O)OC)c1</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>COC(=O)c1cc(C(C)=O)ccc1O</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>C10H10O4</t>
+        </is>
+      </c>
+      <c r="M68" t="n">
+        <v>194.19</v>
+      </c>
+      <c r="N68" t="n">
+        <v>194.0579</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0</v>
+      </c>
+      <c r="P68" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="R68" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="S68" t="n">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
+      </c>
+      <c r="V68" t="n">
+        <v>14</v>
+      </c>
+      <c r="W68" t="n">
+        <v>1</v>
+      </c>
+      <c r="X68" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>XLSMGNNWSRNTIQ-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>img/QFDOS-112_5_acetilsalicilato_de_metilo.png</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>Producto del paso 2: esterificación de Fischer con metanol y HCl. Paso aparentemente accesorio y en realidad imprescindible: el carboxilato libre no es reducible de forma útil por el LiAlH4 y además interferiría en la etapa de alquilación. Convertido en éster metílico, será la fuente del grupo -CH2OH del salbutamol. Sin entrada en ChEMBL; validado con RDKit. CAS no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>QFDOS-113</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5-(Bromoacetil)salicilato de metilo</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Methyl 5-(bromoacetyl)salicylate</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Sintesis del salbutamol</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Intermedio de sintesis</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>COC(=O)c1cc(C(=O)CBr)ccc1O</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>COC(=O)c1cc(C(=O)CBr)ccc1O</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>COC(=O)c1cc(C(=O)CBr)ccc1O</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>C10H9BrO4</t>
+        </is>
+      </c>
+      <c r="M69" t="n">
+        <v>273.08</v>
+      </c>
+      <c r="N69" t="n">
+        <v>271.9684</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>57.57</v>
+      </c>
+      <c r="R69" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>4</v>
+      </c>
+      <c r="U69" t="n">
+        <v>3</v>
+      </c>
+      <c r="V69" t="n">
+        <v>15</v>
+      </c>
+      <c r="W69" t="n">
+        <v>1</v>
+      </c>
+      <c r="X69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>YRPHNSODVHXAOP-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>img/QFDOS-113_5_bromoacetil_salicilato_de_metilo.png</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>Producto del paso 3: bromación en alfa con Br2 a través del enol. Alfa-halocetona, electrófilo excelente para la SN2 siguiente: el orbital pi* del carbonilo estabiliza el estado de transición y acelera la sustitución en órdenes de magnitud frente a un haluro de alquilo primario equivalente. El bromuro sale con configuración electrónica de capa cerrada. Sin entrada en ChEMBL; validado con RDKit. CAS no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>QFDOS-114</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>N-Bencil-terc-butilamina</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>N-Benzyl-tert-butylamine</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Sintesis del salbutamol</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Reactivo: amina nucleófila</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>3378-72-1</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>CC(C)(C)NCc1ccccc1</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>CC(C)(C)[NH2+]Cc1ccccc1</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>CC(C)(C)NCc1ccccc1</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>C11H17N</t>
+        </is>
+      </c>
+      <c r="M70" t="n">
+        <v>163.26</v>
+      </c>
+      <c r="N70" t="n">
+        <v>163.1361</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="R70" t="n">
+        <v>12.03</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>2</v>
+      </c>
+      <c r="V70" t="n">
+        <v>12</v>
+      </c>
+      <c r="W70" t="n">
+        <v>1</v>
+      </c>
+      <c r="X70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.706</v>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>DLSOILHAKCBARI-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC70" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>img/QFDOS-114_n_bencil_terc_butilamina.png</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>Reactivo del paso 4 y una de las decisiones de diseño más instructivas de la ruta. No se emplea terc-butilamina, que es primaria: su producto de alquilación sería una amina secundaria todavía nucleófila, que volvería a atacar la bromocetona y daría mezcla de mono y dialquilado. Al usar la amina secundaria N-bencilada el producto es terciario y la reacción se detiene sola. El bencilo actúa a la vez de grupo protector y de controlador de la sustitución, y se retira después por hidrogenólisis. CAS no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>QFDOS-115</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Alfa-aminocetona N-bencilada (intermedio de alquilación)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>N-Benzyl alpha-aminoketone intermediate</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Sintesis del salbutamol</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Intermedio de sintesis</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>COC(=O)c1cc(C(=O)CN(Cc2ccccc2)C(C)(C)C)ccc1O</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>COC(=O)c1cc(C(=O)CN(Cc2ccccc2)C(C)(C)C)ccc1O</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>COC(=O)c1cc(C(=O)CN(Cc2ccccc2)C(C)(C)C)ccc1O</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>C21H25NO4</t>
+        </is>
+      </c>
+      <c r="M71" t="n">
+        <v>355.43</v>
+      </c>
+      <c r="N71" t="n">
+        <v>355.1784</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>100.38</v>
+      </c>
+      <c r="R71" t="n">
+        <v>66.84</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>5</v>
+      </c>
+      <c r="U71" t="n">
+        <v>6</v>
+      </c>
+      <c r="V71" t="n">
+        <v>26</v>
+      </c>
+      <c r="W71" t="n">
+        <v>2</v>
+      </c>
+      <c r="X71" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>aquiral</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>ZWUVPRCHDWGKFC-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>img/QFDOS-115_alfa_aminocetona_n_bencilada_intermedio_de_alquilacion.png</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>Producto del paso 4: SN2 de la N-bencil-terc-butilamina (QFDOS-114) sobre el carbono que soporta el bromo en QFDOS-113. Amina terciaria, incapaz de seguir alquilando. Conserva intactos los dos grupos que el LiAlH4 va a reducir a continuación: la cetona y el éster metílico aromático. Amina terciaria muy impedida; a pH 7.4 se representa neutra porque es un intermedio de fase orgánica. Sin entrada en ChEMBL; validado con RDKit. CAS no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>QFDOS-116</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>N-Bencilsalbutamol</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>N-Benzylsalbutamol</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sintesis del salbutamol</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Intermedio de sintesis</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>OCc1cc(C(O)CN(Cc2ccccc2)C(C)(C)C)ccc1O</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>OCc1cc(C(O)C[NH+](Cc2ccccc2)C(C)(C)C)ccc1O</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>CC(C)(C)N(Cc1ccccc1)CC(O)c1ccc(O)c(CO)c1</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>C20H27NO3</t>
+        </is>
+      </c>
+      <c r="M72" t="n">
+        <v>329.44</v>
+      </c>
+      <c r="N72" t="n">
+        <v>329.1991</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>95.59</v>
+      </c>
+      <c r="R72" t="n">
+        <v>63.93</v>
+      </c>
+      <c r="S72" t="n">
+        <v>3</v>
+      </c>
+      <c r="T72" t="n">
+        <v>4</v>
+      </c>
+      <c r="U72" t="n">
+        <v>6</v>
+      </c>
+      <c r="V72" t="n">
+        <v>24</v>
+      </c>
+      <c r="W72" t="n">
+        <v>2</v>
+      </c>
+      <c r="X72" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.761</v>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>1 centro(s) sin definir</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>NZBXAYHLQSMNQS-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>img/QFDOS-116_n_bencilsalbutamol.png</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>Producto del paso 5, la etapa clave: el LiAlH4 en THF hace dos reducciones simultáneas. La cetona pasa a alcohol secundario, creando el estereocentro bencílico del farmacóforo como racemato, y el éster metílico aromático pasa a alcohol primario, generando el -CH2OH que da al salbutamol su resistencia a la COMT. El NaBH4 no sirve aquí: reduce la cetona pero no el éster, y el producto quedaría sin el hidroximetilo. El paso 6 (H2, Pd/C) retira el bencilo por hidrogenólisis y libera el fármaco. Sin entrada en ChEMBL; validado con RDKit. CAS no verificado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>QFDOS-117</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Terbutalina</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Terbutaline</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Agonistas beta2 de accion prolongada</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Resorcinol</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>CHEMBL1760</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>CC(C)(C)NCC(O)c1cc(O)cc(O)c1</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>CC(C)(C)[NH2+]CC(O)c1cc(O)cc(O)c1</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>CC(C)(C)NCC(O)c1cc(O)cc(O)c1</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>C12H19NO3</t>
+        </is>
+      </c>
+      <c r="M73" t="n">
+        <v>225.29</v>
+      </c>
+      <c r="N73" t="n">
+        <v>225.1365</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>62.49</v>
+      </c>
+      <c r="R73" t="n">
+        <v>72.72</v>
+      </c>
+      <c r="S73" t="n">
+        <v>4</v>
+      </c>
+      <c r="T73" t="n">
+        <v>4</v>
+      </c>
+      <c r="U73" t="n">
+        <v>3</v>
+      </c>
+      <c r="V73" t="n">
+        <v>16</v>
+      </c>
+      <c r="W73" t="n">
+        <v>1</v>
+      </c>
+      <c r="X73" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>1 centro(s) sin definir</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>XWTYSIMOBUGWOL-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC73" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>img/QFDOS-117_terbutalina.png</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>SABA contemporáneo del salbutamol y segunda solución independiente al mismo problema. Mantiene el terc-butilo sobre el nitrógeno, que aporta selectividad beta2 y resistencia a la MAO, pero resuelve la COMT de otra forma: conserva dos fenoles verdaderos y cambia su posición relativa de 3,4 (catecol) a 3,5 (resorcinol). La COMT requiere la disposición orto porque los dos oxígenos quelan de forma bidentada el Mg2+ del centro activo; en un resorcinol están demasiado separados para quelar y no se forma el complejo catalítico. Par SAR obligado con el salbutamol (QFDOS-074): misma propiedad, distinto mecanismo estructural. Racemato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>QFDOS-118</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Salbutamol analogo hidroxipropilico</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Salbutamol hydroxypropyl analog</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Agonistas adrenergicos directos</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Saligenina</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>CC(C)(C)NCC(O)c1ccc(O)c(CCCO)c1</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>CC(C)(C)[NH2+]CC(O)c1ccc(O)c(CCCO)c1</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>CC(C)(C)NCC(O)c1ccc(O)c(CCCO)c1</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>C15H25NO3</t>
+        </is>
+      </c>
+      <c r="M74" t="n">
+        <v>267.37</v>
+      </c>
+      <c r="N74" t="n">
+        <v>267.1834</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>76.23</v>
+      </c>
+      <c r="R74" t="n">
+        <v>72.72</v>
+      </c>
+      <c r="S74" t="n">
+        <v>4</v>
+      </c>
+      <c r="T74" t="n">
+        <v>4</v>
+      </c>
+      <c r="U74" t="n">
+        <v>6</v>
+      </c>
+      <c r="V74" t="n">
+        <v>19</v>
+      </c>
+      <c r="W74" t="n">
+        <v>1</v>
+      </c>
+      <c r="X74" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>1 centro(s) sin definir</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>KOSZAZQXZVVFJH-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
+          <t>img/QFDOS-118_salbutamol_analogo_hidroxipropilico.png</t>
+        </is>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>Término inactivo que cierra la serie de homólogos 3-OH / 3-CH2OH / 3-CH2CH2OH / 3-(CH2)3OH y fija el límite del volumen de unión. Con tres carbonos de espaciador el hidroxilo queda proyectado fuera de la cavidad, ya no alcanza el aceptor del receptor y la cadena introduce impedimento estérico: la actividad se pierde. Completa el par docente con QFDOS-077 (análogo hidroxietílico, activo). Lección de diseño: es resistente a la COMT como el salbutamol, pero la resistencia metabólica no sirve de nada si antes se ha perdido la afinidad. Sin entrada en ChEMBL; validado con RDKit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>QFDOS-119</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Salbutamol 4-O-sulfato</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Salbutamol 4-O-sulfate</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Metabolismo de agonistas beta2</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Metabolito de fase II</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>CC(C)(C)NCC(O)c1ccc(OS(=O)(=O)O)c(CO)c1</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>CC(C)(C)[NH2+]CC(O)c1ccc(OS(=O)(=O)[O-])c(CO)c1</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>CC(C)(C)NCC(O)c1ccc(OS(=O)(=O)O)c(CO)c1</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>C13H21NO6S</t>
+        </is>
+      </c>
+      <c r="M75" t="n">
+        <v>319.38</v>
+      </c>
+      <c r="N75" t="n">
+        <v>319.109</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>77.26000000000001</v>
+      </c>
+      <c r="R75" t="n">
+        <v>116.09</v>
+      </c>
+      <c r="S75" t="n">
+        <v>4</v>
+      </c>
+      <c r="T75" t="n">
+        <v>6</v>
+      </c>
+      <c r="U75" t="n">
+        <v>6</v>
+      </c>
+      <c r="V75" t="n">
+        <v>21</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>1 centro(s) sin definir</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>FPMLHYFHLRTRMB-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
+          <t>img/QFDOS-119_salbutamol_4_o_sulfato.png</t>
+        </is>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>Metabolito principal del salbutamol y su vía de inactivación real. Al no ser catecol, el salbutamol escapa de la COMT, pero la sulfotransferasa SULT1A3 esterifica con sulfato el fenol en posición 4. El conjugado es inactivo y muy polar, listo para excreción renal. La SULT1A3 se expresa intensamente en la pared intestinal, de modo que la vía oral sufre un metabolismo presistémico intenso y la biodisponibilidad ronda el 50 %: razón farmacocinética, además de la local, para administrarlo inhalado. La enzima es estereoselectiva y sulfata el (S) mucho más despacio que el (R), lo que sustenta el argumento del levosalbutamol (QFDOS-075). Sin entrada en ChEMBL; validado con RDKit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>QFDOS-120</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Salmeterol</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Salmeterol</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Agonistas beta2 de accion prolongada</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Saligenina</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>CHEMBL1263</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>OCc1cc(C(O)CNCCCCCCOCCCCc2ccccc2)ccc1O</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>OCc1cc(C(O)C[NH2+]CCCCCCOCCCCc2ccccc2)ccc1O</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>OCc1cc(C(O)CNCCCCCCOCCCCc2ccccc2)ccc1O</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>C25H37NO4</t>
+        </is>
+      </c>
+      <c r="M76" t="n">
+        <v>415.57</v>
+      </c>
+      <c r="N76" t="n">
+        <v>415.2723</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>120.53</v>
+      </c>
+      <c r="R76" t="n">
+        <v>81.95</v>
+      </c>
+      <c r="S76" t="n">
+        <v>4</v>
+      </c>
+      <c r="T76" t="n">
+        <v>5</v>
+      </c>
+      <c r="U76" t="n">
+        <v>16</v>
+      </c>
+      <c r="V76" t="n">
+        <v>30</v>
+      </c>
+      <c r="W76" t="n">
+        <v>2</v>
+      </c>
+      <c r="X76" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>1 centro(s) sin definir</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>GIIZNNXWQWCKIB-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
+          <t>img/QFDOS-120_salmeterol.png</t>
+        </is>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>Primer LABA, con unas 12 horas de acción (Serevent, aprobado en 1994). Conserva intacta la cabeza saligenínica del salbutamol (3-CH2OH, 4-OH) y sustituye el terc-butilo por una cadena de fenilbutoxihexilo: veinte átomos de cola donde antes había cuatro carbonos. La duración se explica por la hipótesis del exositio: la cola se aloja en un sitio extracelular secundario, fuera del bolsillo ortostérico, y retiene la molécula mientras la cabeza entra y sale del centro activo. Su tamaño y lipofilia explican también el inicio lento. Agonista parcial. Se maneja como racemato; el eutómero es el (R).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>QFDOS-121</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Formoterol</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Formoterol</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Agonistas beta2 de accion prolongada</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Formanilida</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>CHEMBL1256786</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>COc1ccc(CC(C)NCC(O)c2ccc(O)c(NC=O)c2)cc1</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>COc1ccc(CC(C)[NH2+]CC(O)c2ccc(O)c(NC=O)c2)cc1</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>COc1ccc(CC(C)NCC(O)c2ccc(O)c(NC=O)c2)cc1</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>C19H24N2O4</t>
+        </is>
+      </c>
+      <c r="M77" t="n">
+        <v>344.41</v>
+      </c>
+      <c r="N77" t="n">
+        <v>344.1736</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>96.92</v>
+      </c>
+      <c r="R77" t="n">
+        <v>90.81999999999999</v>
+      </c>
+      <c r="S77" t="n">
+        <v>4</v>
+      </c>
+      <c r="T77" t="n">
+        <v>5</v>
+      </c>
+      <c r="U77" t="n">
+        <v>9</v>
+      </c>
+      <c r="V77" t="n">
+        <v>25</v>
+      </c>
+      <c r="W77" t="n">
+        <v>2</v>
+      </c>
+      <c r="X77" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2 centro(s) sin definir</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>BPZSYCZIITTYBL-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>img/QFDOS-121_formoterol.png</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>LABA con la combinación clínicamente más valiosa: inicio rápido y 12 horas de duración, lo que permite usarlo de mantenimiento y de rescate. Agonista completo, a diferencia del salmeterol. Cambia las dos regiones a la vez: el 3-OH pasa a formamido (-NHCHO), que sigue siendo donador y aceptor de enlace de hidrógeno y cae dentro del volumen tolerado sin ser sustrato de la COMT, y el nitrógeno lleva un 1-metil-2-(4-metoxifenil)etilo de lipofilia intermedia. La duración se atribuye al modelo de difusión en la microfase lipídica: el fármaco se reparte hacia la bicapa, forma un depósito y vuelve a ocupar el receptor por difusión lateral. Dos estereocentros; se comercializa como racemato (R,R)/(S,S).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>QFDOS-122</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Arformoterol ((R,R)-Formoterol)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Arformoterol</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Agonistas beta2 de accion prolongada</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Formanilida</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>CHEMBL1363</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>COc1ccc(C[C@@H](C)NC[C@H](O)c2ccc(O)c(NC=O)c2)cc1</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>COc1ccc(C[C@@H](C)[NH2+]C[C@H](O)c2ccc(O)c(NC=O)c2)cc1</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>COc1ccc(C[C@@H](C)NC[C@H](O)c2ccc(O)c(NC=O)c2)cc1</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>C19H24N2O4</t>
+        </is>
+      </c>
+      <c r="M78" t="n">
+        <v>344.41</v>
+      </c>
+      <c r="N78" t="n">
+        <v>344.1736</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>96.92</v>
+      </c>
+      <c r="R78" t="n">
+        <v>90.81999999999999</v>
+      </c>
+      <c r="S78" t="n">
+        <v>4</v>
+      </c>
+      <c r="T78" t="n">
+        <v>5</v>
+      </c>
+      <c r="U78" t="n">
+        <v>9</v>
+      </c>
+      <c r="V78" t="n">
+        <v>25</v>
+      </c>
+      <c r="W78" t="n">
+        <v>2</v>
+      </c>
+      <c r="X78" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>C8:R; C12:R</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>BPZSYCZIITTYBL-YJYMSZOUSA-N</t>
+        </is>
+      </c>
+      <c r="AC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE78" t="inlineStr">
+        <is>
+          <t>img/QFDOS-122_arformoterol_r_r_formoterol.png</t>
+        </is>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>Eutómero (R,R) del formoterol, comercializado aislado (Brovana, 2006). Con dos centros estereogénicos son posibles cuatro estereoisómeros, pero la síntesis se controla para dar solo el par (R,R)/(S,S); el aislamiento del (R,R) es el paso siguiente. La configuración (R) en el carbono bencílico responde a la misma exigencia del ajuste en tres puntos de Easson-Stedman que en toda la familia. Par docente con QFDOS-121 para discutir racemato frente a enantiómero puro, junto con el caso del salbutamol y el levosalbutamol (QFDOS-074 / QFDOS-075).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>QFDOS-123</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Procaterol</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Procaterol</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Agonistas beta2 de accion prolongada</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Quinolinona (bioisostero de catecol)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>CHEMBL160519</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>CCC(NC(C)C)C(O)c1ccc(O)c2[nH]c(=O)ccc12</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>CCC([NH2+]C(C)C)C(O)c1ccc(O)c2[nH]c(=O)ccc12</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>CCC(NC(C)C)C(O)c1ccc(O)c2[nH]c(=O)ccc12</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>C16H22N2O3</t>
+        </is>
+      </c>
+      <c r="M79" t="n">
+        <v>290.36</v>
+      </c>
+      <c r="N79" t="n">
+        <v>290.163</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>83.54000000000001</v>
+      </c>
+      <c r="R79" t="n">
+        <v>85.34999999999999</v>
+      </c>
+      <c r="S79" t="n">
+        <v>4</v>
+      </c>
+      <c r="T79" t="n">
+        <v>4</v>
+      </c>
+      <c r="U79" t="n">
+        <v>5</v>
+      </c>
+      <c r="V79" t="n">
+        <v>21</v>
+      </c>
+      <c r="W79" t="n">
+        <v>2</v>
+      </c>
+      <c r="X79" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2 centro(s) sin definir</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>FKNXQNWAXFXVNW-UHFFFAOYSA-N</t>
+        </is>
+      </c>
+      <c r="AC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE79" t="inlineStr">
+        <is>
+          <t>img/QFDOS-123_procaterol.png</t>
+        </is>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>Precedente histórico del bioisosterismo heterocíclico que después usarán indacaterol y olodaterol. Sustituye el catecol por una 8-hidroxiquinolin-2(1H)-ona: el fenol en 8 y el NH lactámico reproducen el patrón de donadores del catecol en disposición espacial equivalente, sin patrón orto y por tanto sin reconocimiento por la COMT. Conserva el etilo en alfa de la isoetarina (QFDOS-073) y el N-isopropilo. Demuestra que la cabeza aromática admite sustitución completa por un heterociclo siempre que se conserve el juego de enlaces de hidrógeno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>QFDOS-124</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Indacaterol</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Indacaterol</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Agonistas beta2 de accion prolongada</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Quinolinona (bioisostero de catecol)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>CHEMBL1095777</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>CCc1cc2c(cc1CC)CC(NC[C@H](O)c1ccc(O)c3[nH]c(=O)ccc13)C2</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>CCc1cc2c(cc1CC)CC([NH2+]C[C@H](O)c1ccc(O)c3[nH]c(=O)ccc13)C2</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>CCc1cc2c(cc1CC)CC(NC[C@H](O)c1ccc(O)c3[nH]c(=O)ccc13)C2</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>C24H28N2O3</t>
+        </is>
+      </c>
+      <c r="M80" t="n">
+        <v>392.5</v>
+      </c>
+      <c r="N80" t="n">
+        <v>392.21</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>115.59</v>
+      </c>
+      <c r="R80" t="n">
+        <v>85.34999999999999</v>
+      </c>
+      <c r="S80" t="n">
+        <v>4</v>
+      </c>
+      <c r="T80" t="n">
+        <v>4</v>
+      </c>
+      <c r="U80" t="n">
+        <v>6</v>
+      </c>
+      <c r="V80" t="n">
+        <v>29</v>
+      </c>
+      <c r="W80" t="n">
+        <v>4</v>
+      </c>
+      <c r="X80" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>C15:R</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>QZZUEBNBZAPZLX-QFIPXVFZSA-N</t>
+        </is>
+      </c>
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE80" t="inlineStr">
+        <is>
+          <t>img/QFDOS-124_indacaterol.png</t>
+        </is>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>Ultra-LABA de 24 horas y dosis única diaria (Onbrez, 2009). Cabeza de 8-hidroxiquinolin-2(1H)-ona, bioisóstero no clásico del catecol: no se sustituye átomo por átomo sino función de reconocimiento por función de reconocimiento. Tres ventajas simultáneas sobre el catecol: resistencia absoluta a la COMT por ausencia de patrón orto; rigidez conformacional del sistema bicíclico fusionado, que reduce la penalización entrópica de la unión; y mayor lipofilia, que favorece la retención en la microfase lipídica pulmonar. Sobre el nitrógeno, un 5,6-dietilindan-2-ilo rígido y voluminoso. Configuración (R) en el carbono bencílico.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>QFDOS-125</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Olodaterol</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Olodaterol</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Agonistas beta2 de accion prolongada</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Benzoxazinona (bioisostero de catecol)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>CHEMBL605846</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>COc1ccc(CC(C)(C)NC[C@H](O)c2cc(O)cc3c2OCC(=O)N3)cc1</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>COc1ccc(CC(C)(C)[NH2+]C[C@H](O)c2cc(O)cc3c2OCC(=O)N3)cc1</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>COc1ccc(CC(C)(C)NC[C@H](O)c2cc(O)cc3c2OCC(=O)N3)cc1</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>C21H26N2O5</t>
+        </is>
+      </c>
+      <c r="M81" t="n">
+        <v>386.45</v>
+      </c>
+      <c r="N81" t="n">
+        <v>386.1842</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>105.97</v>
+      </c>
+      <c r="R81" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="S81" t="n">
+        <v>4</v>
+      </c>
+      <c r="T81" t="n">
+        <v>6</v>
+      </c>
+      <c r="U81" t="n">
+        <v>7</v>
+      </c>
+      <c r="V81" t="n">
+        <v>28</v>
+      </c>
+      <c r="W81" t="n">
+        <v>3</v>
+      </c>
+      <c r="X81" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>C13:R</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>COUYJEVMBVSIHV-SFHVURJKSA-N</t>
+        </is>
+      </c>
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>img/QFDOS-125_olodaterol.png</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>Ultra-LABA de 24 horas (Striverdi Respimat, 2014). Aplica la misma estrategia que el indacaterol con otro heterociclo: una 6-hidroxi-2H-1,4-benzoxazin-3(4H)-ona sustituida en 8. El fenol y el NH lactámico reproducen el patrón de donadores del catecol y el anillo queda fuera del alcance de la COMT. Sobre el nitrógeno, un terc-alquilo con metoxifenilo. Agonista casi completo y muy potente. Configuración (R). Par SAR con el indacaterol (QFDOS-124): dos heterociclos distintos resolviendo el mismo problema con la misma lógica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>QFDOS-126</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Vilanterol</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Vilanterol</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Agonistas beta2 de accion prolongada</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Saligenina</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>CHEMBL1198857</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>OCc1cc([C@@H](O)CNCCCCCCOCCOCc2c(Cl)cccc2Cl)ccc1O</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>OCc1cc([C@@H](O)C[NH2+]CCCCCCOCCOCc2c(Cl)cccc2Cl)ccc1O</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>1</v>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>OCc1cc([C@@H](O)CNCCCCCCOCCOCc2c(Cl)cccc2Cl)ccc1O</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>C24H33Cl2NO5</t>
+        </is>
+      </c>
+      <c r="M82" t="n">
+        <v>486.44</v>
+      </c>
+      <c r="N82" t="n">
+        <v>485.1736</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>4.61</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>127.26</v>
+      </c>
+      <c r="R82" t="n">
+        <v>91.18000000000001</v>
+      </c>
+      <c r="S82" t="n">
+        <v>4</v>
+      </c>
+      <c r="T82" t="n">
+        <v>6</v>
+      </c>
+      <c r="U82" t="n">
+        <v>16</v>
+      </c>
+      <c r="V82" t="n">
+        <v>32</v>
+      </c>
+      <c r="W82" t="n">
+        <v>2</v>
+      </c>
+      <c r="X82" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>C6:R</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>DAFYYTQWSAWIGS-DEOSSOPVSA-N</t>
+        </is>
+      </c>
+      <c r="AC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD82" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="AE82" t="inlineStr">
+        <is>
+          <t>img/QFDOS-126_vilanterol.png</t>
+        </is>
+      </c>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>Ultra-LABA de 24 horas (2013), empleado siempre en combinación fija. A diferencia de indacaterol y olodaterol, no cambia la cabeza: conserva la saligenina del salbutamol y del salmeterol y lleva toda la duración en la cola, un éter largo rematado por un 2,6-diclorobencilo. Cierra el argumento del bloque: las 24 horas se alcanzan por dos caminos independientes, rediseñando la cabeza aromática (indacaterol, olodaterol) o alargando y afinando la cola lipofílica (salmeterol, vilanterol). Configuración (R); se formula como trifenatato.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AF50"/>
+  <autoFilter ref="A1:AF82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8216,7 +13024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -8923,7 +13731,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>C13H17NO2</t>
+          <t>C14H19NO2</t>
         </is>
       </c>
     </row>
@@ -8940,7 +13748,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>C12H17NO2</t>
+          <t>C13H19NO2</t>
         </is>
       </c>
     </row>
@@ -8957,7 +13765,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>C12H17NO2</t>
+          <t>C13H19NO2</t>
         </is>
       </c>
     </row>
@@ -9077,6 +13885,550 @@
       <c r="C50" t="inlineStr">
         <is>
           <t>C10H14N2O4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="155" customHeight="1">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>QFDOS-095</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1,2-Diclorobenceno</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>C6H4Cl2</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="155" customHeight="1">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>QFDOS-096</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Cloruro de acetilo</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>C2H3ClO</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="155" customHeight="1">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>QFDOS-097</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>3,4-Dicloroacetofenona</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>C8H6Cl2O</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="155" customHeight="1">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>QFDOS-098</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Bromo</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Br2</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="155" customHeight="1">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>QFDOS-099</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2-Bromo-3,4-dicloroacetofenona</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>C8H5BrCl2O</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="155" customHeight="1">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>QFDOS-100</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2-Bromo-1-(3,4-diclorofenil)etanol</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>C8H7BrCl2O</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="155" customHeight="1">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>QFDOS-101</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Isopropilamina</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>C3H9N</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="155" customHeight="1">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>QFDOS-102</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2-Acetilnaftaleno</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>C12H10O</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="155" customHeight="1">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>QFDOS-103</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1-Naftol</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>C10H8O</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="155" customHeight="1">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>QFDOS-104</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Epiclorhidrina</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>C3H5ClO</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="155" customHeight="1">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>QFDOS-105</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1-Naftil glicidil éter</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>C13H12O2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="155" customHeight="1">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>QFDOS-106</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Catecol</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>C6H6O2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="155" customHeight="1">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>QFDOS-107</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2-Hidroximetil-1,4-benzodioxano</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>C9H10O3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="155" customHeight="1">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>QFDOS-108</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2-Clorometil-1,4-benzodioxano</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>C9H9ClO2</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="155" customHeight="1">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>QFDOS-109</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Piperidina</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>C5H11N</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="155" customHeight="1">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>QFDOS-110</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ácido acetilsalicílico (Aspirina)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>C9H8O4</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="155" customHeight="1">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>QFDOS-111</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Ácido 5-acetil-2-hidroxibenzoico</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>C9H8O4</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="155" customHeight="1">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>QFDOS-112</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>5-Acetilsalicilato de metilo</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>C10H10O4</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="155" customHeight="1">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>QFDOS-113</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5-(Bromoacetil)salicilato de metilo</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>C10H9BrO4</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="155" customHeight="1">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>QFDOS-114</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>N-Bencil-terc-butilamina</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>C11H17N</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="155" customHeight="1">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>QFDOS-115</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Alfa-aminocetona N-bencilada (intermedio de alquilación)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>C21H25NO4</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="155" customHeight="1">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>QFDOS-116</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>N-Bencilsalbutamol</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>C20H27NO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="155" customHeight="1">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>QFDOS-117</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Terbutalina</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>C12H19NO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="155" customHeight="1">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>QFDOS-118</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Salbutamol analogo hidroxipropilico</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>C15H25NO3</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="155" customHeight="1">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>QFDOS-119</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Salbutamol 4-O-sulfato</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>C13H21NO6S</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="155" customHeight="1">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>QFDOS-120</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Salmeterol</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>C25H37NO4</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="155" customHeight="1">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>QFDOS-121</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Formoterol</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>C19H24N2O4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="155" customHeight="1">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>QFDOS-122</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Arformoterol ((R,R)-Formoterol)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>C19H24N2O4</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="155" customHeight="1">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>QFDOS-123</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Procaterol</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>C16H22N2O3</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="155" customHeight="1">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>QFDOS-124</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Indacaterol</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>C24H28N2O3</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="155" customHeight="1">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>QFDOS-125</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Olodaterol</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>C21H26N2O5</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="155" customHeight="1">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>QFDOS-126</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Vilanterol</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>C24H33Cl2NO5</t>
         </is>
       </c>
     </row>
